--- a/data/trans_orig/IP3107-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3107-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33372</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>39126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46408</t>
+          <t>45865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67726</t>
+          <t>68321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>31918</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66250</t>
+          <t>65417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82842</t>
+          <t>83884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62835</t>
+          <t>63421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81529</t>
+          <t>82254</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135228</t>
+          <t>134570</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158751</t>
+          <t>160003</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26440</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>43151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30760</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48649</t>
+          <t>48619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62938</t>
+          <t>63488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88467</t>
+          <t>86818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31547</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109178</t>
+          <t>109356</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127818</t>
+          <t>127664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109786</t>
+          <t>109919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129199</t>
+          <t>129716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224770</t>
+          <t>224054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251855</t>
+          <t>252333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>30342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>15049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>13981</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23431</t>
+          <t>23066</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80303</t>
+          <t>80615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94676</t>
+          <t>94731</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98090</t>
+          <t>98071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112271</t>
+          <t>112778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>183431</t>
+          <t>182887</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>202063</t>
+          <t>203530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>28027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31891</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33586</t>
+          <t>34031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53469</t>
+          <t>53682</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17637</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24536</t>
+          <t>23709</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129973</t>
+          <t>130066</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>149378</t>
+          <t>149639</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126140</t>
+          <t>126383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>144864</t>
+          <t>144732</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>262073</t>
+          <t>263540</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288938</t>
+          <t>289539</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78594</t>
+          <t>79134</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>106757</t>
+          <t>109013</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>87700</t>
+          <t>88405</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>117374</t>
+          <t>117344</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>176059</t>
+          <t>176062</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>217683</t>
+          <t>218551</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24484</t>
+          <t>24506</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48542</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48210</t>
+          <t>47935</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51740</t>
+          <t>53540</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>65198</t>
+          <t>64425</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>91809</t>
+          <t>91791</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29934</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31999</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>51868</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>403712</t>
+          <t>403989</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>438196</t>
+          <t>440301</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>414669</t>
+          <t>413917</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>450237</t>
+          <t>450797</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>831372</t>
+          <t>831745</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>879904</t>
+          <t>882105</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,99%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>21036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22163</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37801</t>
+          <t>35915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,47 +4537,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>11211</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>6120</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>18696</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>2,39%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>11211</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>6132</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>18170</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>26552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>35979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>83683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100376</t>
+          <t>100219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71313</t>
+          <t>71719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90711</t>
+          <t>91681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160583</t>
+          <t>162161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>185836</t>
+          <t>187169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26883</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45839</t>
+          <t>46006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>18678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23570</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25703</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43846</t>
+          <t>43209</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25504</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121928</t>
+          <t>121127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140430</t>
+          <t>139815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128448</t>
+          <t>128264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148395</t>
+          <t>147891</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254508</t>
+          <t>255942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>282811</t>
+          <t>283838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>18358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32249</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16430</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92263</t>
+          <t>92800</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106215</t>
+          <t>106874</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,82 +6205,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>74,49%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>85,79%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>103642</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>95344</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>111477</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>75,93%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>69,85%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>81,67%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>203534</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>193360</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>213554</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>77,96%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>74,06%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>85,26%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>103642</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>95015</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>110863</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>75,93%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>69,61%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>203534</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>193052</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>213826</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>77,96%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>73,95%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25397</t>
+          <t>26431</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27978</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>126751</t>
+          <t>126535</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144945</t>
+          <t>144552</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>129523</t>
+          <t>129392</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147607</t>
+          <t>146933</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>262404</t>
+          <t>262978</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>286647</t>
+          <t>286039</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>36836</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57548</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63639</t>
+          <t>62958</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>83277</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113915</t>
+          <t>112578</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27347</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31670</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>54585</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48776</t>
+          <t>49339</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,77 +7343,77 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>61246</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>50708</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>75125</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>100539</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>86176</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>117875</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
           <t>8,18%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>61246</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>49793</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>74688</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>100539</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>85162</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>117881</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48065</t>
+          <t>49539</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52214</t>
+          <t>53079</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77622</t>
+          <t>78887</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>443985</t>
+          <t>443536</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>477341</t>
+          <t>476741</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>444075</t>
+          <t>444648</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>479606</t>
+          <t>480679</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>898583</t>
+          <t>897740</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>947008</t>
+          <t>947279</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25376</t>
+          <t>26236</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20843</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>36205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81635</t>
+          <t>81639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97771</t>
+          <t>98553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89390</t>
+          <t>89287</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105913</t>
+          <t>106759</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177486</t>
+          <t>176096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200496</t>
+          <t>200435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21324</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>17699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31486</t>
+          <t>32059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25301</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>36114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136706</t>
+          <t>136632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>154515</t>
+          <t>154398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156867</t>
+          <t>155792</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174672</t>
+          <t>174062</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299769</t>
+          <t>299430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324079</t>
+          <t>323625</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14535</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115344</t>
+          <t>115262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126954</t>
+          <t>127616</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125598</t>
+          <t>125342</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140625</t>
+          <t>140225</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245332</t>
+          <t>245346</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>264688</t>
+          <t>264088</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>18817</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>15557</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30376</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148061</t>
+          <t>149072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>164801</t>
+          <t>165348</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147700</t>
+          <t>147971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164101</t>
+          <t>164058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>302280</t>
+          <t>302656</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>326394</t>
+          <t>325654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46291</t>
+          <t>47152</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26202</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59543</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>86109</t>
+          <t>86789</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17977</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13971</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>28237</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45708</t>
+          <t>46188</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70650</t>
+          <t>71106</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>61835</t>
+          <t>61441</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>30133</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52594</t>
+          <t>51116</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77207</t>
+          <t>77170</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>106558</t>
+          <t>107081</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>501825</t>
+          <t>501461</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>533015</t>
+          <t>532190</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>537648</t>
+          <t>538165</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>571964</t>
+          <t>571222</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1048934</t>
+          <t>1045306</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1094573</t>
+          <t>1092909</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
